--- a/resultados/third_review/20260907_data2024_medication_combinations.xlsx
+++ b/resultados/third_review/20260907_data2024_medication_combinations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">medications</t>
   </si>
@@ -32,15 +32,15 @@
     <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 30 MG INJECTABLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
   </si>
   <si>
@@ -59,82 +62,88 @@
     <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 60 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 10 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LANREOTIDE 60 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 60 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCTREOTIDE 0.1 MG/ML INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 60 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 60 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCTREOTIDE 0.1 MG/ML INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 60 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 60 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 10 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">LANREOTIDE 60 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">OCTREOTIDE 0.1 MG/ML INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -479,7 +488,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>1497</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +496,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>596</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +504,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>583</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>517</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +520,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>222</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7">
@@ -519,7 +528,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +536,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9">
@@ -535,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -543,7 +552,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +560,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -559,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +576,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -575,7 +584,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -583,7 +592,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +600,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -599,7 +608,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +616,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -615,7 +624,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -623,7 +632,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +640,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -639,7 +648,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -647,7 +656,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -655,7 +664,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +672,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -671,7 +680,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -679,7 +688,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -695,7 +704,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -703,7 +712,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -711,7 +720,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -727,7 +736,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -735,7 +744,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -743,7 +752,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -751,7 +760,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -791,6 +800,30 @@
         <v>41</v>
       </c>
       <c r="B41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="n">
         <v>4231</v>
       </c>
     </row>
